--- a/artfynd/A 23504-2023 artfynd.xlsx
+++ b/artfynd/A 23504-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23504-2023 artfynd.xlsx
+++ b/artfynd/A 23504-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>112182880</v>
       </c>
       <c r="B2" t="n">
-        <v>96692</v>
+        <v>98092</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567436</v>
+        <v>567437</v>
       </c>
       <c r="R2" t="n">
         <v>6820974</v>

--- a/artfynd/A 23504-2023 artfynd.xlsx
+++ b/artfynd/A 23504-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>112182880</v>
       </c>
       <c r="B2" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 23504-2023 artfynd.xlsx
+++ b/artfynd/A 23504-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>112182880</v>
       </c>
       <c r="B2" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 23504-2023 artfynd.xlsx
+++ b/artfynd/A 23504-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>112182880</v>
       </c>
       <c r="B2" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 23504-2023 artfynd.xlsx
+++ b/artfynd/A 23504-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>112182880</v>
       </c>
       <c r="B2" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>219790</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 23504-2023 artfynd.xlsx
+++ b/artfynd/A 23504-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>112182880</v>
       </c>
       <c r="B2" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>219790</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 23504-2023 artfynd.xlsx
+++ b/artfynd/A 23504-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>112182880</v>
       </c>
       <c r="B2" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 23504-2023 artfynd.xlsx
+++ b/artfynd/A 23504-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>112182880</v>
       </c>
       <c r="B2" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 23504-2023 artfynd.xlsx
+++ b/artfynd/A 23504-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>112182880</v>
       </c>
       <c r="B2" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 23504-2023 artfynd.xlsx
+++ b/artfynd/A 23504-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>112182880</v>
       </c>
       <c r="B2" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 23504-2023 artfynd.xlsx
+++ b/artfynd/A 23504-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>112182880</v>
       </c>
       <c r="B2" t="n">
-        <v>98161</v>
+        <v>98264</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 23504-2023 artfynd.xlsx
+++ b/artfynd/A 23504-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112182880</v>
+        <v>127893978</v>
       </c>
       <c r="B2" t="n">
-        <v>98264</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>100053</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,19 +708,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Acktjärnbo, Hls</t>
+          <t>Bollnäs kommun, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567437</v>
+        <v>567429</v>
       </c>
       <c r="R2" t="n">
-        <v>6820974</v>
+        <v>6820933</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,31 +779,30 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Johan Möller</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>113888492</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -894,6 +898,112 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>112182880</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Acktjärnbo, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>567437</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6820974</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Arbrå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23504-2023 artfynd.xlsx
+++ b/artfynd/A 23504-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127893978</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888492</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,8 +1019,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112182880</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>